--- a/rainfall_output/rainfall_2026-08-29.xlsx
+++ b/rainfall_output/rainfall_2026-08-29.xlsx
@@ -469,7 +469,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3">
@@ -517,7 +517,7 @@
         <v>1.7</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="5">
@@ -541,7 +541,7 @@
         <v>2.2</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="6">
@@ -585,8 +585,12 @@
       <c r="D7" t="n">
         <v>74.64</v>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -608,9 +612,7 @@
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -629,9 +631,7 @@
       <c r="D9" t="n">
         <v>74.77</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
         <v>0</v>
       </c>
@@ -681,7 +681,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
@@ -725,8 +725,12 @@
       <c r="D13" t="n">
         <v>74.09</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -749,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -773,7 +777,7 @@
         <v>0.5</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16">
@@ -793,12 +797,8 @@
       <c r="D16" t="n">
         <v>73.48999999999999</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -821,7 +821,7 @@
         <v>0.5</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="18">
@@ -845,7 +845,7 @@
         <v>5.5</v>
       </c>
       <c r="F18" t="n">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="19">
@@ -868,7 +868,9 @@
       <c r="E19" t="n">
         <v>0</v>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -887,9 +889,11 @@
       <c r="D20" t="n">
         <v>75.23999999999999</v>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>1.7</v>
+      </c>
       <c r="F20" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="21">
@@ -913,7 +917,7 @@
         <v>9.4</v>
       </c>
       <c r="F21" t="n">
-        <v>10.4</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -937,7 +941,7 @@
         <v>5.2</v>
       </c>
       <c r="F22" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="23">
@@ -960,9 +964,7 @@
       <c r="E23" t="n">
         <v>2.9</v>
       </c>
-      <c r="F23" t="n">
-        <v>3.4</v>
-      </c>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -984,9 +986,7 @@
       <c r="E24" t="n">
         <v>1.9</v>
       </c>
-      <c r="F24" t="n">
-        <v>5.4</v>
-      </c>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1005,10 +1005,10 @@
       <c r="D25" t="n">
         <v>74.19</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1030,7 +1030,9 @@
       <c r="E26" t="n">
         <v>4.6</v>
       </c>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1049,7 +1051,9 @@
       <c r="D27" t="n">
         <v>73.69</v>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
@@ -1075,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="29">
@@ -1099,7 +1103,7 @@
         <v>5.1</v>
       </c>
       <c r="F29" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="30">
@@ -1123,7 +1127,7 @@
         <v>3.5</v>
       </c>
       <c r="F30" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1147,7 +1151,7 @@
         <v>0.7</v>
       </c>
       <c r="F31" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="32">
@@ -1167,10 +1171,10 @@
       <c r="D32" t="n">
         <v>75.65000000000001</v>
       </c>
-      <c r="E32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1190,9 +1194,7 @@
         <v>74.87</v>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1239,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="36">
@@ -1263,7 +1265,7 @@
         <v>0.7</v>
       </c>
       <c r="F36" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="37">
@@ -1287,7 +1289,7 @@
         <v>3.6</v>
       </c>
       <c r="F37" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="38">
@@ -1311,7 +1313,7 @@
         <v>0.3</v>
       </c>
       <c r="F38" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="39">
@@ -1331,8 +1333,12 @@
       <c r="D39" t="n">
         <v>76.93000000000001</v>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1354,9 +1360,7 @@
       <c r="E40" t="n">
         <v>0.3</v>
       </c>
-      <c r="F40" t="n">
-        <v>3</v>
-      </c>
+      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1378,9 +1382,7 @@
       <c r="E41" t="n">
         <v>0.3</v>
       </c>
-      <c r="F41" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1399,9 +1401,7 @@
       <c r="D42" t="n">
         <v>75.38</v>
       </c>
-      <c r="E42" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
         <v>0.7</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>5</v>
       </c>
       <c r="F44" t="n">
-        <v>4.8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45">
@@ -1471,8 +1471,12 @@
       <c r="D45" t="n">
         <v>75.12</v>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F45" t="n">
+        <v>6.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
